--- a/data/trans_orig/P33_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P33_R-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36926</t>
+          <t>37860</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>65067</t>
+          <t>66740</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>43468</t>
+          <t>44790</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>70824</t>
+          <t>71131</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,47 +783,47 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
+          <t>9,64%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>15,31%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>107134</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>89018</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>128482</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>11,25%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
           <t>9,35%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>15,24%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>107134</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>88640</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>126712</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>11,25%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>9,31%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,49%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>422614</t>
+          <t>420941</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>450755</t>
+          <t>449821</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>393859</t>
+          <t>393552</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>421215</t>
+          <t>419893</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,47 +896,47 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
+          <t>90,36%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>870</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>845230</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>823882</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>863346</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>88,75%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>86,51%</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
           <t>90,65%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>870</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>845230</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>825652</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>863724</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>88,75%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>86,69%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>90,69%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>69771</t>
+          <t>70464</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>107888</t>
+          <t>106438</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>77220</t>
+          <t>79057</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>114631</t>
+          <t>113563</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>158675</t>
+          <t>159759</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>212702</t>
+          <t>210868</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,65%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>618367</t>
+          <t>619817</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>656484</t>
+          <t>655791</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>506296</t>
+          <t>507364</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>543707</t>
+          <t>541870</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1134480</t>
+          <t>1136314</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1188507</t>
+          <t>1187423</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,14%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>82847</t>
+          <t>84341</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>120275</t>
+          <t>122091</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>96926</t>
+          <t>95621</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>136688</t>
+          <t>136097</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>191329</t>
+          <t>191836</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>247880</t>
+          <t>244376</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,61%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>505689</t>
+          <t>503873</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>543117</t>
+          <t>541623</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,79%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>550203</t>
+          <t>550794</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>589965</t>
+          <t>591270</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,1%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1064975</t>
+          <t>1068479</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1121526</t>
+          <t>1121019</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>85,39%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>71590</t>
+          <t>70694</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>108691</t>
+          <t>107079</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>91512</t>
+          <t>89679</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>127416</t>
+          <t>128516</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>171631</t>
+          <t>170091</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>225062</t>
+          <t>224668</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,92%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>403639</t>
+          <t>405251</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>440740</t>
+          <t>441636</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>79,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>385168</t>
+          <t>384068</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>421072</t>
+          <t>422905</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>799852</t>
+          <t>800246</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>853283</t>
+          <t>854823</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>78,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>83,4%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>65532</t>
+          <t>66147</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>97290</t>
+          <t>97154</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>91955</t>
+          <t>90712</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>125135</t>
+          <t>123955</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>164646</t>
+          <t>164189</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>211928</t>
+          <t>210165</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>26,87%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>283958</t>
+          <t>284094</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>315716</t>
+          <t>315101</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>74,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>275733</t>
+          <t>276913</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>308913</t>
+          <t>310156</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,78%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>77,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>570188</t>
+          <t>571951</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>617470</t>
+          <t>617927</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>79,01%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>87489</t>
+          <t>88952</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>120284</t>
+          <t>120587</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>130263</t>
+          <t>129261</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>164020</t>
+          <t>163693</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>226223</t>
+          <t>225048</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>273695</t>
+          <t>272364</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>35,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>43,37%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>169489</t>
+          <t>169186</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>202284</t>
+          <t>200821</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>58,49%</t>
+          <t>58,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>174179</t>
+          <t>174506</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>207936</t>
+          <t>208938</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>51,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>61,48%</t>
+          <t>61,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>354276</t>
+          <t>355607</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>401748</t>
+          <t>402923</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>56,42%</t>
+          <t>56,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>63,98%</t>
+          <t>64,16%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>72965</t>
+          <t>73949</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>99900</t>
+          <t>101507</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>35,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>158077</t>
+          <t>158370</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>197580</t>
+          <t>198420</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>47,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>59,34%</t>
+          <t>59,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>239446</t>
+          <t>241664</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>288070</t>
+          <t>290622</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>44,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>53,88%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>106453</t>
+          <t>104846</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>133388</t>
+          <t>132404</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>51,59%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>64,16%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>135407</t>
+          <t>134567</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>174910</t>
+          <t>174617</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>52,53%</t>
+          <t>52,44%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>251270</t>
+          <t>248718</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>299894</t>
+          <t>297676</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>55,19%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>555227</t>
+          <t>554047</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>646675</t>
+          <t>649763</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>760929</t>
+          <t>761366</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>858862</t>
+          <t>861081</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1342973</t>
+          <t>1338686</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1474587</t>
+          <t>1468943</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,3%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2582930</t>
+          <t>2579842</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2674378</t>
+          <t>2675558</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2498276</t>
+          <t>2496057</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2596209</t>
+          <t>2595772</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>74,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5112156</t>
+          <t>5117800</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5243770</t>
+          <t>5248057</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>77,7%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>79,68%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>57632</t>
+          <t>57177</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>88367</t>
+          <t>86403</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>81181</t>
+          <t>80730</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>117568</t>
+          <t>116149</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>145838</t>
+          <t>147555</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>194000</t>
+          <t>191776</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>21,76%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>363861</t>
+          <t>365825</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>394596</t>
+          <t>395051</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>311699</t>
+          <t>313118</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>348086</t>
+          <t>348537</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,61%</t>
+          <t>72,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>81,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>687494</t>
+          <t>689718</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>735656</t>
+          <t>733939</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,99%</t>
+          <t>78,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,26%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>112083</t>
+          <t>113939</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>155466</t>
+          <t>154862</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>107006</t>
+          <t>106756</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>147569</t>
+          <t>147612</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>229668</t>
+          <t>232872</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>288902</t>
+          <t>297727</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,98%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>530684</t>
+          <t>531288</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>574067</t>
+          <t>572211</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>77,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>461622</t>
+          <t>461579</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>502185</t>
+          <t>502435</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1006439</t>
+          <t>997614</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1065673</t>
+          <t>1062469</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>77,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>82,02%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>123921</t>
+          <t>122027</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>168288</t>
+          <t>169459</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>137417</t>
+          <t>138956</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>184857</t>
+          <t>186621</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>275672</t>
+          <t>275173</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>337168</t>
+          <t>337415</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,31%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>510735</t>
+          <t>509564</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>555102</t>
+          <t>556996</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>82,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>524042</t>
+          <t>522278</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>571482</t>
+          <t>569943</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>73,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1050754</t>
+          <t>1050507</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1112250</t>
+          <t>1112749</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>80,17%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>140667</t>
+          <t>138403</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>186694</t>
+          <t>186341</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>178527</t>
+          <t>180169</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>229863</t>
+          <t>229438</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>333403</t>
+          <t>334120</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>402009</t>
+          <t>402993</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,8%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>425871</t>
+          <t>426224</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>471898</t>
+          <t>474162</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>69,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>77,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>386336</t>
+          <t>386761</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>437672</t>
+          <t>436030</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>62,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,03%</t>
+          <t>70,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>826755</t>
+          <t>825771</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>895361</t>
+          <t>894644</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>67,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>72,81%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>95185</t>
+          <t>93794</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>132596</t>
+          <t>132242</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>160594</t>
+          <t>160819</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>204701</t>
+          <t>205259</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>269542</t>
+          <t>267330</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>325803</t>
+          <t>324467</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>37,17%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>294484</t>
+          <t>294838</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>331895</t>
+          <t>333286</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,95%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>241050</t>
+          <t>240492</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>285157</t>
+          <t>284932</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>547028</t>
+          <t>548364</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>603289</t>
+          <t>605501</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,67%</t>
+          <t>62,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>69,37%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>123290</t>
+          <t>123006</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>161319</t>
+          <t>159875</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>51,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>147402</t>
+          <t>145816</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>183820</t>
+          <t>180911</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>51,23%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>279860</t>
+          <t>281465</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>333470</t>
+          <t>333929</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>50,37%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>148467</t>
+          <t>149911</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>186496</t>
+          <t>186780</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>48,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>60,2%</t>
+          <t>60,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>169285</t>
+          <t>172194</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>205703</t>
+          <t>207289</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>48,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>329422</t>
+          <t>328963</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>383032</t>
+          <t>381427</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>57,54%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>99778</t>
+          <t>100350</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>133421</t>
+          <t>133966</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>54,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>199960</t>
+          <t>197753</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>239010</t>
+          <t>236955</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>51,73%</t>
+          <t>51,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>61,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>310121</t>
+          <t>307001</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>359159</t>
+          <t>362025</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>48,97%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>57,17%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>113307</t>
+          <t>112762</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>146950</t>
+          <t>146378</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>45,7%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>147535</t>
+          <t>149590</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>186585</t>
+          <t>188792</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>48,84%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>274114</t>
+          <t>271248</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>323152</t>
+          <t>326272</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>51,52%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>832387</t>
+          <t>826532</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>941945</t>
+          <t>934936</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1099157</t>
+          <t>1094611</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1219663</t>
+          <t>1216383</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1952772</t>
+          <t>1968252</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2111054</t>
+          <t>2120077</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,45%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2471615</t>
+          <t>2478624</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2581173</t>
+          <t>2587028</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>72,61%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>75,79%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2329295</t>
+          <t>2332575</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2449801</t>
+          <t>2454347</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>65,73%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4851463</t>
+          <t>4842440</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5009745</t>
+          <t>4994265</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>71,73%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>53958</t>
+          <t>54504</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>85107</t>
+          <t>86235</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>59406</t>
+          <t>59111</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>90802</t>
+          <t>90521</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>120512</t>
+          <t>123237</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>164210</t>
+          <t>165052</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,27%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>334356</t>
+          <t>333228</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>365505</t>
+          <t>364959</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>79,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>304005</t>
+          <t>304286</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>335401</t>
+          <t>335696</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>650060</t>
+          <t>649218</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>693758</t>
+          <t>691033</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>84,87%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>86123</t>
+          <t>86625</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>124920</t>
+          <t>124856</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>70477</t>
+          <t>71336</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>103534</t>
+          <t>105184</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>166927</t>
+          <t>167261</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>217975</t>
+          <t>217884</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,91%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>465576</t>
+          <t>465640</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>504373</t>
+          <t>503871</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,84%</t>
+          <t>78,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>458181</t>
+          <t>456531</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>491238</t>
+          <t>490379</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>81,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>934236</t>
+          <t>934327</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>985284</t>
+          <t>984950</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,48%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>109923</t>
+          <t>110226</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>153728</t>
+          <t>150982</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>119823</t>
+          <t>118662</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>161399</t>
+          <t>158921</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>242313</t>
+          <t>240141</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>300493</t>
+          <t>299373</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,53%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>513782</t>
+          <t>516528</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>557587</t>
+          <t>557284</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>77,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>499987</t>
+          <t>502465</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>541563</t>
+          <t>542724</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>82,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1028403</t>
+          <t>1029523</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1086583</t>
+          <t>1088755</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>77,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>81,93%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>111257</t>
+          <t>113536</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>155627</t>
+          <t>156337</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>156064</t>
+          <t>153551</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>202007</t>
+          <t>200767</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>278128</t>
+          <t>281373</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>345301</t>
+          <t>345358</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,78%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>488161</t>
+          <t>487451</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>532531</t>
+          <t>530252</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>444006</t>
+          <t>445246</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>489949</t>
+          <t>492462</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,73%</t>
+          <t>68,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>944499</t>
+          <t>944442</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1011672</t>
+          <t>1008427</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>73,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>78,18%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>99147</t>
+          <t>97727</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>140145</t>
+          <t>138025</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>152059</t>
+          <t>151348</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>195743</t>
+          <t>195217</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>258342</t>
+          <t>258942</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>318398</t>
+          <t>319592</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,86%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>336579</t>
+          <t>338699</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>377577</t>
+          <t>378997</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>79,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>300060</t>
+          <t>300586</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>343744</t>
+          <t>344455</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,52%</t>
+          <t>60,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>69,33%</t>
+          <t>69,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>654130</t>
+          <t>652936</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>714186</t>
+          <t>713586</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>67,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>73,37%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>104737</t>
+          <t>104748</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>140472</t>
+          <t>140605</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>157520</t>
+          <t>158241</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>197971</t>
+          <t>197358</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>42,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>52,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>275269</t>
+          <t>273166</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>327193</t>
+          <t>325903</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>45,83%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>193858</t>
+          <t>193725</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>229593</t>
+          <t>229582</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>57,98%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>178822</t>
+          <t>179435</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>219273</t>
+          <t>218552</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>47,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>58,19%</t>
+          <t>58,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>383930</t>
+          <t>385220</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>435854</t>
+          <t>437957</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>53,99%</t>
+          <t>54,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>61,59%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>95069</t>
+          <t>94278</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>124147</t>
+          <t>122982</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>48,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>159301</t>
+          <t>157527</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>202945</t>
+          <t>203822</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>51,58%</t>
+          <t>51,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>260559</t>
+          <t>263949</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>315376</t>
+          <t>316258</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>48,75%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>131126</t>
+          <t>132291</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>160204</t>
+          <t>160995</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>51,82%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>62,76%</t>
+          <t>63,07%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>190540</t>
+          <t>189663</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>234184</t>
+          <t>235958</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>48,42%</t>
+          <t>48,2%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>59,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>333382</t>
+          <t>332500</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>388199</t>
+          <t>384809</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>51,39%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>59,84%</t>
+          <t>59,31%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>728777</t>
+          <t>735103</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>834909</t>
+          <t>838273</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>951601</t>
+          <t>952532</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1062651</t>
+          <t>1062267</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1718801</t>
+          <t>1716459</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1871601</t>
+          <t>1870789</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>27,04%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2552675</t>
+          <t>2549311</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2658807</t>
+          <t>2652481</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>75,25%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>78,49%</t>
+          <t>78,3%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2467351</t>
+          <t>2467735</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2578401</t>
+          <t>2577470</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>69,91%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5045986</t>
+          <t>5046798</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5198786</t>
+          <t>5201128</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>72,96%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>75,19%</t>
         </is>
       </c>
     </row>
@@ -9665,32 +9665,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>33352</t>
+          <t>33786</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16434</t>
+          <t>17869</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>59632</t>
+          <t>55537</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>45925</t>
+          <t>58437</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31265</t>
+          <t>41207</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>64326</t>
+          <t>78857</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>79277</t>
+          <t>92224</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>56513</t>
+          <t>67278</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>109269</t>
+          <t>119782</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,21%</t>
         </is>
       </c>
     </row>
@@ -9778,32 +9778,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>337835</t>
+          <t>350085</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>311555</t>
+          <t>328334</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>354753</t>
+          <t>366002</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>260133</t>
+          <t>296578</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>241732</t>
+          <t>276158</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>274793</t>
+          <t>313808</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>77,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>597969</t>
+          <t>646662</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>567977</t>
+          <t>619104</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>620733</t>
+          <t>671608</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>83,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>90,89%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>371187</t>
+          <t>383871</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>371187</t>
+          <t>383871</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>371187</t>
+          <t>383871</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>306058</t>
+          <t>355015</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>306058</t>
+          <t>355015</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>306058</t>
+          <t>355015</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>677246</t>
+          <t>738886</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>677246</t>
+          <t>738886</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>677246</t>
+          <t>738886</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>63803</t>
+          <t>66899</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45957</t>
+          <t>50125</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>83884</t>
+          <t>87992</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>89724</t>
+          <t>96431</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>53314</t>
+          <t>79032</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>114897</t>
+          <t>117213</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>153526</t>
+          <t>163330</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>117969</t>
+          <t>139154</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>183378</t>
+          <t>196338</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,68%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>342922</t>
+          <t>393448</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>322841</t>
+          <t>372355</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>360768</t>
+          <t>410222</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>411731</t>
+          <t>392715</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>386558</t>
+          <t>371933</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>448141</t>
+          <t>410114</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>76,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>754654</t>
+          <t>786163</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>724802</t>
+          <t>753155</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>790211</t>
+          <t>810339</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>79,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>85,34%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>406725</t>
+          <t>460347</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>406725</t>
+          <t>460347</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>406725</t>
+          <t>460347</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>501455</t>
+          <t>489146</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>501455</t>
+          <t>489146</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>501455</t>
+          <t>489146</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>908180</t>
+          <t>949493</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>908180</t>
+          <t>949493</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>908180</t>
+          <t>949493</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>106694</t>
+          <t>119669</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>86764</t>
+          <t>100513</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>124523</t>
+          <t>141779</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>119740</t>
+          <t>139214</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>105182</t>
+          <t>122380</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>136256</t>
+          <t>157144</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>226434</t>
+          <t>258884</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>204009</t>
+          <t>231642</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>252748</t>
+          <t>286826</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>23,84%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>416628</t>
+          <t>486038</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>398799</t>
+          <t>463928</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>436558</t>
+          <t>505194</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>80,24%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,21%</t>
+          <t>76,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>401150</t>
+          <t>458004</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>384634</t>
+          <t>440074</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>415708</t>
+          <t>474838</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>76,69%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>817778</t>
+          <t>944041</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>791464</t>
+          <t>916099</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>840203</t>
+          <t>971283</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>80,74%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>523322</t>
+          <t>605707</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>523322</t>
+          <t>605707</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>523322</t>
+          <t>605707</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>520890</t>
+          <t>597218</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>520890</t>
+          <t>597218</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>520890</t>
+          <t>597218</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1044212</t>
+          <t>1202925</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1044212</t>
+          <t>1202925</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1044212</t>
+          <t>1202925</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>178328</t>
+          <t>190383</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>84351</t>
+          <t>165939</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>260208</t>
+          <t>217190</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>189220</t>
+          <t>206172</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>156964</t>
+          <t>188396</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>210174</t>
+          <t>224921</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>367548</t>
+          <t>396556</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>215080</t>
+          <t>362561</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>449670</t>
+          <t>427595</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>30,38%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>694979</t>
+          <t>494555</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>613099</t>
+          <t>467748</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>788956</t>
+          <t>518999</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>72,2%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>68,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>509880</t>
+          <t>516585</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>488926</t>
+          <t>497836</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>542136</t>
+          <t>534361</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>72,93%</t>
+          <t>71,47%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>68,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>73,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1204858</t>
+          <t>1011140</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1122736</t>
+          <t>980101</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1357326</t>
+          <t>1045135</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>71,83%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>69,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>74,24%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>873307</t>
+          <t>684938</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>873307</t>
+          <t>684938</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>873307</t>
+          <t>684938</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>699100</t>
+          <t>722757</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>699100</t>
+          <t>722757</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>699100</t>
+          <t>722757</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1572406</t>
+          <t>1407696</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1572406</t>
+          <t>1407696</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1572406</t>
+          <t>1407696</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>158129</t>
+          <t>171953</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>139258</t>
+          <t>152302</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>181450</t>
+          <t>194012</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>205557</t>
+          <t>228373</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>188999</t>
+          <t>210264</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>221246</t>
+          <t>245941</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>363686</t>
+          <t>400327</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>339635</t>
+          <t>370768</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>392469</t>
+          <t>429030</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>36,29%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>387837</t>
+          <t>421482</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>364516</t>
+          <t>399423</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>406708</t>
+          <t>441133</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>71,02%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>67,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>74,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>321948</t>
+          <t>360415</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>306259</t>
+          <t>342847</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>338506</t>
+          <t>378524</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>61,21%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>58,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,17%</t>
+          <t>64,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>709785</t>
+          <t>781896</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>681002</t>
+          <t>753193</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>733836</t>
+          <t>811455</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>66,14%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,44%</t>
+          <t>63,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>68,64%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>545966</t>
+          <t>593435</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>545966</t>
+          <t>593435</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>545966</t>
+          <t>593435</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>527505</t>
+          <t>588788</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>527505</t>
+          <t>588788</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>527505</t>
+          <t>588788</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1073471</t>
+          <t>1182223</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1073471</t>
+          <t>1182223</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1073471</t>
+          <t>1182223</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>126155</t>
+          <t>139933</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>112044</t>
+          <t>124562</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>140333</t>
+          <t>155327</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>364379</t>
+          <t>172431</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>235972</t>
+          <t>159129</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>501476</t>
+          <t>187519</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>490535</t>
+          <t>312364</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>355216</t>
+          <t>292304</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>732302</t>
+          <t>333861</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>40,23%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>236808</t>
+          <t>260761</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>222630</t>
+          <t>245367</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>250919</t>
+          <t>276132</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>65,24%</t>
+          <t>65,08%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>61,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>234498</t>
+          <t>256824</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>97401</t>
+          <t>241736</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>362905</t>
+          <t>270126</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>59,83%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>56,32%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>62,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>471305</t>
+          <t>517585</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>229538</t>
+          <t>496088</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>606624</t>
+          <t>537645</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>62,36%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>63,07%</t>
+          <t>64,78%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>362963</t>
+          <t>400694</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>362963</t>
+          <t>400694</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>362963</t>
+          <t>400694</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>598877</t>
+          <t>429255</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>598877</t>
+          <t>429255</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>598877</t>
+          <t>429255</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>961840</t>
+          <t>829949</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>961840</t>
+          <t>829949</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>961840</t>
+          <t>829949</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>108240</t>
+          <t>117622</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>95500</t>
+          <t>104112</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>122389</t>
+          <t>130747</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>43,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>196451</t>
+          <t>212014</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>182017</t>
+          <t>196864</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>210668</t>
+          <t>227519</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>48,03%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>51,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>304691</t>
+          <t>329636</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>286479</t>
+          <t>309773</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>323816</t>
+          <t>349770</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>44,49%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>41,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>47,76%</t>
+          <t>47,21%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>165169</t>
+          <t>181870</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>151020</t>
+          <t>168745</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>177909</t>
+          <t>195380</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>56,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>65,07%</t>
+          <t>65,24%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>208114</t>
+          <t>229408</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>193897</t>
+          <t>213903</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>222548</t>
+          <t>244558</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>48,46%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>55,01%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>373283</t>
+          <t>411279</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>354158</t>
+          <t>391145</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>391495</t>
+          <t>431142</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>55,51%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>52,24%</t>
+          <t>52,79%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>57,74%</t>
+          <t>58,19%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>273409</t>
+          <t>299492</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>273409</t>
+          <t>299492</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>273409</t>
+          <t>299492</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>404565</t>
+          <t>441422</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>404565</t>
+          <t>441422</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>404565</t>
+          <t>441422</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>677974</t>
+          <t>740915</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>677974</t>
+          <t>740915</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>677974</t>
+          <t>740915</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>774702</t>
+          <t>840246</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>592845</t>
+          <t>787282</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>863876</t>
+          <t>894029</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1210995</t>
+          <t>1113074</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1047790</t>
+          <t>1066597</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1664509</t>
+          <t>1169690</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1985697</t>
+          <t>1953320</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1757557</t>
+          <t>1879397</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2464388</t>
+          <t>2023902</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>28,7%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2582177</t>
+          <t>2588239</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2493003</t>
+          <t>2534456</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2764034</t>
+          <t>2641203</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>75,49%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>73,92%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2347455</t>
+          <t>2510528</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1893941</t>
+          <t>2453912</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2510660</t>
+          <t>2557005</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>53,22%</t>
+          <t>67,72%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>70,57%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>4929632</t>
+          <t>5098767</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4450941</t>
+          <t>5028185</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5157772</t>
+          <t>5172690</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>72,3%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>73,35%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3356879</t>
+          <t>3428485</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3356879</t>
+          <t>3428485</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3356879</t>
+          <t>3428485</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3558450</t>
+          <t>3623602</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3558450</t>
+          <t>3623602</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3558450</t>
+          <t>3623602</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>6915329</t>
+          <t>7052087</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>6915329</t>
+          <t>7052087</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>6915329</t>
+          <t>7052087</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
